--- a/backend/scripts/audit-output/expeditor-smoke/ex-4.0.1.xlsx
+++ b/backend/scripts/audit-output/expeditor-smoke/ex-4.0.1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <si>
     <t>Дата</t>
   </si>
@@ -105,7 +105,7 @@
     <t>Итог:</t>
   </si>
   <si>
-    <t>Загрузочный лист 4.0.1 (Время печати: 27.05.2026 19:51:40)</t>
+    <t>Загрузочный лист 4.0.1 (Время печати: 28.05.2026 17:37:19)</t>
   </si>
   <si>
     <t xml:space="preserve">Бренд </t>
@@ -787,8 +787,8 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AD20"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <dimension ref="A1:AN20"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.4" customWidth="1"/>
     <col min="2" max="2" width="7.4" customWidth="1"/>
@@ -798,10 +798,10 @@
     <col min="6" max="6" width="28.6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -813,10 +813,10 @@
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
         <v>3</v>
@@ -831,7 +831,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
         <v>7</v>
@@ -846,7 +846,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
         <v>10</v>
@@ -861,7 +861,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
         <v>12</v>
@@ -876,7 +876,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
         <v>15</v>
@@ -891,7 +891,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
         <v>17</v>
@@ -906,7 +906,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
         <v>19</v>
@@ -921,7 +921,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
         <v>21</v>
@@ -936,7 +936,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
         <v>24</v>
@@ -951,7 +951,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
@@ -959,8 +959,8 @@
         <v>10083400</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25"/>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25"/>
@@ -968,7 +968,7 @@
     <row r="20" spans="1:30" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>
 
@@ -978,7 +978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AD20"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
@@ -1215,7 +1215,7 @@
     <mergeCell ref="D14:G14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>
 
@@ -1225,7 +1225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AD20"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
@@ -1455,7 +1455,7 @@
     <mergeCell ref="D14:G14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>
 
@@ -1465,7 +1465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AD20"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
@@ -1802,7 +1802,7 @@
     <mergeCell ref="D16:G16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>
 
@@ -1812,7 +1812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AD20"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
@@ -2285,7 +2285,7 @@
     <mergeCell ref="D15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>
 
@@ -2295,7 +2295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AD20"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
@@ -2474,7 +2474,7 @@
     <mergeCell ref="D10:G10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>
 
@@ -2484,7 +2484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AD20"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
@@ -2725,7 +2725,7 @@
     <mergeCell ref="D14:G14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>
 
@@ -2735,7 +2735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AD20"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
@@ -2945,7 +2945,7 @@
     <mergeCell ref="D12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>
 
@@ -2955,7 +2955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AD20"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
@@ -3166,6 +3166,6 @@
     <mergeCell ref="D13:G13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>